--- a/src/main/resources/static/assets/inventario_ejemplo_kardo.xlsx
+++ b/src/main/resources/static/assets/inventario_ejemplo_kardo.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="715" uniqueCount="458">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="715" uniqueCount="459">
   <si>
     <t xml:space="preserve">SKU</t>
   </si>
@@ -147,7 +147,7 @@
     <t xml:space="preserve">2026-10-04</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-28</t>
+    <t xml:space="preserve">2026-10-27</t>
   </si>
   <si>
     <t xml:space="preserve">LAC-GLO-006</t>
@@ -264,657 +264,657 @@
     <t xml:space="preserve">2026-10-12</t>
   </si>
   <si>
+    <t xml:space="preserve">2026-10-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LAC-GLO-012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7750101001128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crema de Leche Gloria UHT 200ml</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-CRM-2607A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2027-04-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BEB-INC-001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7750102002019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gaseosa Inca Kola Sabor Original 500ml</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BEBIDAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-IK-500-26A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2027-07-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BEB-INC-002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7750102002026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gaseosa Inca Kola Sin Azucar 500ml</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-IK-ZERO-26B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2027-07-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BEB-COC-003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7750102002033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gaseosa Coca Cola Sabor Original 500ml</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-CC-500-26A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BEB-COC-004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7750102002040</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gaseosa Coca Cola Sin Azucar 500ml</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-CC-ZERO-26B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2027-07-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BEB-INC-005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7750102002057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gaseosa Inca Kola Gordita Vidrio 750ml</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-IK-GOR-26C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2027-08-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BEB-SPR-006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7750102002064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gaseosa Sprite Lima-Limon 500ml</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-SP-500-26A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2027-07-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BEB-SLU-007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7750102002071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agua Mineral San Luis Sin Gas 625ml</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-AG-SL-625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2027-10-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BEB-SMA-008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7750102002088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agua Mineral San Mateo con Gas 600ml</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-AG-SM-600</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BEB-SPO-009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7750102002095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bebida Rehidratante Sporade Frutos Rojos 500ml</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-SPO-FR-500</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BEB-GAT-010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7750102002101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bebida Rehidratante Gatorade Cool Blue 500ml</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-GAT-CB-500</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BEB-CIF-011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7750102002118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bebida Citrica Cifrut Granadilla 500ml</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-CIF-GR-500</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2027-05-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BEB-FRU-012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7750102002125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nectar Frugos del Valle Durazno 1L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-FRU-DZ-1L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIC-CUS-001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7750103003016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cerveza Cusquena Dorada Botella 330ml</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LICORES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-CUS-DOR-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIC-CUS-002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7750103003023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cerveza Cusquena Negra Botella 330ml</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-CUS-NEG-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIC-PIL-003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7750103003030</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cerveza Pilsen Callao Botella 630ml</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-PIL-630-26A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIC-PIL-004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7750103003047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cerveza Pilsen Callao Six Pack Lata 355ml</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PACK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-PIL-SIX-26B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2027-08-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIC-CRI-005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7750103003054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cerveza Cristal Botella 650ml</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-CRI-650-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIC-COR-006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7750103003061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cerveza Corona Extra Botella 355ml</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-COR-355-MEX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIC-STE-007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7750103003078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cerveza Stella Artois Botella 330ml</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-STE-330-BEL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2027-08-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIC-CAR-008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7750103003085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ron Cartavio Black Barrel 750ml</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-RON-CAR-BB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2028-10-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIC-GAL-009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7750103003092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pisco Cuatro Gallos Quebranta 700ml</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-PIS-4G-QUE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIC-JOH-010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7750103003108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Whisky Johnnie Walker Red Label 750ml</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-JW-RED-750</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2029-07-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SNK-LAY-001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7750104004013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Papas Fritas Lays Clasicas 160g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SNACKS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BOLSA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-LAY-CLA-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2027-01-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SNK-LAY-002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7750104004020</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Papas Fritas Lays Onduladas 150g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-LAY-OND-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-12-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SNK-DOR-003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7750104004037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tortillas de Maiz Doritos Mega Queso 150g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-DOR-QSO-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2027-01-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SNK-CHI-004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7750104004044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Snack de Maiz Chizitos Fiesta 140g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-CHZ-FIE-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-12-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SNK-PIQ-005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7750104004051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Piqueo Snax Familiar 200g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-PIQ-SNX-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2027-01-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SNK-CHI-006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7750104004068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chifle Piurano Salado Karinto 120g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-CHF-KAR-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-12-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SNK-SUB-007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7750104004075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chocolate Sublime Clasico Tableta 30g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UNIDAD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-SUB-CLA-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2027-05-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SNK-PRI-008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7750104004082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chocolate Princesa Crema de Mani 30g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-PRI-CRE-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2027-04-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SNK-TRI-009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7750104004099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chocolate Triangulo DOnofrio 30g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-TRI-DON-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SNK-MOR-010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7750104004105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Galletas Morochas Rellenas Paquete 6 unid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-MOR-PAQ-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2027-03-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SNK-CAS-011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7750104004112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Galletas Casino Menta Paquete 6 unid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-CAS-MEN-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2027-03-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SNK-PEP-012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7750104004129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Galletas Dona Pepa Field Paquete 6 unid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-DNP-PAQ-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SNK-SOD-013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7750104004136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Galletas Soda Field Paquete 6 unid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-SOD-FIE-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SNK-GOM-014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7750104004143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gomitas Ambrosoli Ositos Dulces 100g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-GOM-OSI-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EMB-SFE-001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7750105005010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hot Dog de Pollo San Fernando 500g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EMBUTIDOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-HD-POL-2610</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EMB-SFE-002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7750105005027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jamonada Especial San Fernando 250g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-JAM-SFE-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EMB-BRA-003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7750105005034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jamonada de Cerdo Braedt 200g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-JAM-BRA-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-11-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EMB-OTT-004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7750105005041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tocino Ahumado Tiras Otto Kunz 180g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-TOC-OTT-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-11-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EMB-SFE-005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7750105005058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chorizo Parrillero San Fernando 400g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-CHO-PAR-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-11-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EMB-PRE-006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7750105005065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Salchicha Huachana La Preferida 250g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-SAL-HUA-26</t>
+  </si>
+  <si>
     <t xml:space="preserve">2026-10-26</t>
   </si>
   <si>
-    <t xml:space="preserve">LAC-GLO-012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7750101001128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Crema de Leche Gloria UHT 200ml</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-CRM-2607A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2027-04-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BEB-INC-001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7750102002019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gaseosa Inca Kola Sabor Original 500ml</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BEBIDAS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-IK-500-26A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2027-07-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BEB-INC-002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7750102002026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gaseosa Inca Kola Sin Azucar 500ml</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-IK-ZERO-26B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2027-07-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BEB-COC-003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7750102002033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gaseosa Coca Cola Sabor Original 500ml</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-CC-500-26A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BEB-COC-004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7750102002040</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gaseosa Coca Cola Sin Azucar 500ml</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-CC-ZERO-26B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2027-07-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BEB-INC-005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7750102002057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gaseosa Inca Kola Gordita Vidrio 750ml</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-IK-GOR-26C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2027-08-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BEB-SPR-006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7750102002064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gaseosa Sprite Lima-Limon 500ml</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-SP-500-26A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2027-07-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BEB-SLU-007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7750102002071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Agua Mineral San Luis Sin Gas 625ml</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-AG-SL-625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2027-10-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BEB-SMA-008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7750102002088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Agua Mineral San Mateo con Gas 600ml</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-AG-SM-600</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BEB-SPO-009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7750102002095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bebida Rehidratante Sporade Frutos Rojos 500ml</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-SPO-FR-500</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BEB-GAT-010</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7750102002101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bebida Rehidratante Gatorade Cool Blue 500ml</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-GAT-CB-500</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BEB-CIF-011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7750102002118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bebida Citrica Cifrut Granadilla 500ml</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-CIF-GR-500</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2027-05-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BEB-FRU-012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7750102002125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nectar Frugos del Valle Durazno 1L</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-FRU-DZ-1L</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIC-CUS-001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7750103003016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cerveza Cusquena Dorada Botella 330ml</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LICORES</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-CUS-DOR-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIC-CUS-002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7750103003023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cerveza Cusquena Negra Botella 330ml</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-CUS-NEG-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIC-PIL-003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7750103003030</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cerveza Pilsen Callao Botella 630ml</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-PIL-630-26A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIC-PIL-004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7750103003047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cerveza Pilsen Callao Six Pack Lata 355ml</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PACK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-PIL-SIX-26B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2027-08-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIC-CRI-005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7750103003054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cerveza Cristal Botella 650ml</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-CRI-650-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIC-COR-006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7750103003061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cerveza Corona Extra Botella 355ml</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-COR-355-MEX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIC-STE-007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7750103003078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cerveza Stella Artois Botella 330ml</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-STE-330-BEL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2027-08-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIC-CAR-008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7750103003085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ron Cartavio Black Barrel 750ml</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-RON-CAR-BB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2028-10-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIC-GAL-009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7750103003092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pisco Cuatro Gallos Quebranta 700ml</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-PIS-4G-QUE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIC-JOH-010</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7750103003108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Whisky Johnnie Walker Red Label 750ml</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-JW-RED-750</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-04-25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2029-07-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SNK-LAY-001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7750104004013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Papas Fritas Lays Clasicas 160g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SNACKS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BOLSA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-LAY-CLA-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2027-01-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SNK-LAY-002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7750104004020</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Papas Fritas Lays Onduladas 150g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-LAY-OND-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-12-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SNK-DOR-003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7750104004037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tortillas de Maiz Doritos Mega Queso 150g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-DOR-QSO-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2027-01-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SNK-CHI-004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7750104004044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Snack de Maiz Chizitos Fiesta 140g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-CHZ-FIE-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-12-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SNK-PIQ-005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7750104004051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Piqueo Snax Familiar 200g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-PIQ-SNX-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2027-01-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SNK-CHI-006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7750104004068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chifle Piurano Salado Karinto 120g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-CHF-KAR-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-12-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SNK-SUB-007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7750104004075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chocolate Sublime Clasico Tableta 30g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UNIDAD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-SUB-CLA-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2027-05-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SNK-PRI-008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7750104004082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chocolate Princesa Crema de Mani 30g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-PRI-CRE-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2027-04-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SNK-TRI-009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7750104004099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chocolate Triangulo DOnofrio 30g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-TRI-DON-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SNK-MOR-010</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7750104004105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Galletas Morochas Rellenas Paquete 6 unid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-MOR-PAQ-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2027-03-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SNK-CAS-011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7750104004112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Galletas Casino Menta Paquete 6 unid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-CAS-MEN-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2027-03-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SNK-PEP-012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7750104004129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Galletas Dona Pepa Field Paquete 6 unid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-DNP-PAQ-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SNK-SOD-013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7750104004136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Galletas Soda Field Paquete 6 unid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-SOD-FIE-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SNK-GOM-014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7750104004143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gomitas Ambrosoli Ositos Dulces 100g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-GOM-OSI-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EMB-SFE-001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7750105005010</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hot Dog de Pollo San Fernando 500g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EMBUTIDOS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-HD-POL-2610</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EMB-SFE-002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7750105005027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jamonada Especial San Fernando 250g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-JAM-SFE-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EMB-BRA-003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7750105005034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jamonada de Cerdo Braedt 200g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-JAM-BRA-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-11-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EMB-OTT-004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7750105005041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tocino Ahumado Tiras Otto Kunz 180g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-TOC-OTT-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-11-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EMB-SFE-005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7750105005058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chorizo Parrillero San Fernando 400g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-CHO-PAR-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-11-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EMB-PRE-006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7750105005065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Salchicha Huachana La Preferida 250g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-SAL-HUA-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-27</t>
-  </si>
-  <si>
     <t xml:space="preserve">EMB-OTT-007</t>
   </si>
   <si>
@@ -978,6 +978,9 @@
     <t xml:space="preserve">2026-10-15</t>
   </si>
   <si>
+    <t xml:space="preserve">2026-10-25</t>
+  </si>
+  <si>
     <t xml:space="preserve">PAN-BIM-003</t>
   </si>
   <si>
@@ -1065,7 +1068,7 @@
     <t xml:space="preserve">2026-10-18</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-25</t>
+    <t xml:space="preserve">2026-10-23</t>
   </si>
   <si>
     <t xml:space="preserve">ABA-COS-001</t>
@@ -3512,7 +3515,7 @@
         <v>320</v>
       </c>
       <c r="J59" t="s">
-        <v>299</v>
+        <v>321</v>
       </c>
       <c r="K59" t="n">
         <v>20</v>
@@ -3520,13 +3523,13 @@
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B60" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C60" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D60" t="s">
         <v>313</v>
@@ -3541,13 +3544,13 @@
         <v>10.50</v>
       </c>
       <c r="H60" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="I60" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="J60" t="s">
-        <v>44</v>
+        <v>299</v>
       </c>
       <c r="K60" t="n">
         <v>18</v>
@@ -3555,13 +3558,13 @@
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B61" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C61" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="D61" t="s">
         <v>313</v>
@@ -3576,13 +3579,13 @@
         <v>5.80</v>
       </c>
       <c r="H61" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="I61" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="J61" t="s">
-        <v>272</v>
+        <v>44</v>
       </c>
       <c r="K61" t="n">
         <v>24</v>
@@ -3590,13 +3593,13 @@
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B62" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C62" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="D62" t="s">
         <v>313</v>
@@ -3611,7 +3614,7 @@
         <v>5.90</v>
       </c>
       <c r="H62" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="I62" t="s">
         <v>315</v>
@@ -3625,13 +3628,13 @@
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B63" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C63" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="D63" t="s">
         <v>313</v>
@@ -3646,13 +3649,13 @@
         <v>4.00</v>
       </c>
       <c r="H63" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="I63" t="s">
         <v>114</v>
       </c>
       <c r="J63" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="K63" t="n">
         <v>30</v>
@@ -3660,13 +3663,13 @@
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B64" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C64" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D64" t="s">
         <v>313</v>
@@ -3681,13 +3684,13 @@
         <v>5.50</v>
       </c>
       <c r="H64" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="I64" t="s">
         <v>94</v>
       </c>
       <c r="J64" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="K64" t="n">
         <v>30</v>
@@ -3695,13 +3698,13 @@
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B65" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C65" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D65" t="s">
         <v>313</v>
@@ -3716,13 +3719,13 @@
         <v>4.50</v>
       </c>
       <c r="H65" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="I65" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="J65" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="K65" t="n">
         <v>20</v>
@@ -3730,16 +3733,16 @@
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B66" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C66" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D66" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="E66" t="s">
         <v>201</v>
@@ -3751,7 +3754,7 @@
         <v>5.30</v>
       </c>
       <c r="H66" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="I66" t="s">
         <v>63</v>
@@ -3765,16 +3768,16 @@
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B67" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C67" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D67" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="E67" t="s">
         <v>201</v>
@@ -3786,7 +3789,7 @@
         <v>5.90</v>
       </c>
       <c r="H67" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="I67" t="s">
         <v>30</v>
@@ -3800,16 +3803,16 @@
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B68" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C68" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D68" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="E68" t="s">
         <v>41</v>
@@ -3821,7 +3824,7 @@
         <v>10.90</v>
       </c>
       <c r="H68" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="I68" t="s">
         <v>17</v>
@@ -3835,16 +3838,16 @@
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B69" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C69" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D69" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="E69" t="s">
         <v>41</v>
@@ -3856,13 +3859,13 @@
         <v>29.90</v>
       </c>
       <c r="H69" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="I69" t="s">
         <v>184</v>
       </c>
       <c r="J69" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="K69" t="n">
         <v>20</v>
@@ -3870,16 +3873,16 @@
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B70" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C70" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D70" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="E70" t="s">
         <v>61</v>
@@ -3891,13 +3894,13 @@
         <v>3.20</v>
       </c>
       <c r="H70" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="I70" t="s">
         <v>23</v>
       </c>
       <c r="J70" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="K70" t="n">
         <v>80</v>
@@ -3905,16 +3908,16 @@
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B71" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C71" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="D71" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="E71" t="s">
         <v>61</v>
@@ -3926,13 +3929,13 @@
         <v>2.80</v>
       </c>
       <c r="H71" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="I71" t="s">
         <v>63</v>
       </c>
       <c r="J71" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="K71" t="n">
         <v>60</v>
@@ -3940,16 +3943,16 @@
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B72" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C72" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="D72" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="E72" t="s">
         <v>15</v>
@@ -3961,7 +3964,7 @@
         <v>6.50</v>
       </c>
       <c r="H72" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="I72" t="s">
         <v>184</v>
@@ -3975,16 +3978,16 @@
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B73" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C73" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D73" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="E73" t="s">
         <v>15</v>
@@ -3996,10 +3999,10 @@
         <v>7.80</v>
       </c>
       <c r="H73" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="I73" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="J73" t="s">
         <v>185</v>
@@ -4010,19 +4013,19 @@
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B74" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C74" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="D74" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="E74" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="F74" t="n">
         <v>6.40</v>
@@ -4031,7 +4034,7 @@
         <v>8.90</v>
       </c>
       <c r="H74" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="I74" t="s">
         <v>36</v>
@@ -4045,19 +4048,19 @@
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B75" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C75" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="D75" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="E75" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="F75" t="n">
         <v>4.20</v>
@@ -4066,7 +4069,7 @@
         <v>5.90</v>
       </c>
       <c r="H75" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="I75" t="s">
         <v>30</v>
@@ -4080,19 +4083,19 @@
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B76" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C76" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="D76" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="E76" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="F76" t="n">
         <v>6.80</v>
@@ -4101,7 +4104,7 @@
         <v>9.50</v>
       </c>
       <c r="H76" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="I76" t="s">
         <v>94</v>
@@ -4115,19 +4118,19 @@
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B77" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C77" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="D77" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="E77" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="F77" t="n">
         <v>12.50</v>
@@ -4136,13 +4139,13 @@
         <v>16.90</v>
       </c>
       <c r="H77" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="I77" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="J77" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="K77" t="n">
         <v>30</v>
@@ -4150,16 +4153,16 @@
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B78" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C78" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="D78" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E78" t="s">
         <v>163</v>
@@ -4171,7 +4174,7 @@
         <v>7.50</v>
       </c>
       <c r="H78" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="I78" t="s">
         <v>30</v>
@@ -4185,16 +4188,16 @@
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B79" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C79" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="D79" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E79" t="s">
         <v>163</v>
@@ -4206,7 +4209,7 @@
         <v>8.50</v>
       </c>
       <c r="H79" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="I79" t="s">
         <v>63</v>
@@ -4220,16 +4223,16 @@
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B80" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C80" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="D80" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E80" t="s">
         <v>163</v>
@@ -4241,7 +4244,7 @@
         <v>6.80</v>
       </c>
       <c r="H80" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="I80" t="s">
         <v>94</v>
@@ -4255,16 +4258,16 @@
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B81" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C81" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="D81" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E81" t="s">
         <v>233</v>
@@ -4276,7 +4279,7 @@
         <v>4.50</v>
       </c>
       <c r="H81" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="I81" t="s">
         <v>17</v>
@@ -4290,16 +4293,16 @@
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B82" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C82" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D82" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E82" t="s">
         <v>233</v>
@@ -4311,7 +4314,7 @@
         <v>4.00</v>
       </c>
       <c r="H82" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="I82" t="s">
         <v>178</v>
@@ -4325,16 +4328,16 @@
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B83" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C83" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="D83" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E83" t="s">
         <v>41</v>
@@ -4346,10 +4349,10 @@
         <v>14.90</v>
       </c>
       <c r="H83" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="I83" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="J83" t="s">
         <v>185</v>
@@ -4360,19 +4363,19 @@
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B84" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C84" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="D84" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E84" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="F84" t="n">
         <v>3.50</v>
@@ -4381,7 +4384,7 @@
         <v>5.00</v>
       </c>
       <c r="H84" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="I84" t="s">
         <v>17</v>
@@ -4395,16 +4398,16 @@
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B85" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C85" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="D85" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E85" t="s">
         <v>41</v>
@@ -4416,7 +4419,7 @@
         <v>4.50</v>
       </c>
       <c r="H85" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="I85" t="s">
         <v>94</v>
@@ -4430,16 +4433,16 @@
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B86" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C86" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="D86" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E86" t="s">
         <v>68</v>
@@ -4451,13 +4454,13 @@
         <v>5.00</v>
       </c>
       <c r="H86" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="I86" t="s">
         <v>63</v>
       </c>
       <c r="J86" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="K86" t="n">
         <v>36</v>
@@ -4465,16 +4468,16 @@
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B87" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C87" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="D87" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E87" t="s">
         <v>41</v>
@@ -4486,13 +4489,13 @@
         <v>5.90</v>
       </c>
       <c r="H87" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="I87" t="s">
         <v>36</v>
       </c>
       <c r="J87" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="K87" t="n">
         <v>36</v>
@@ -4500,16 +4503,16 @@
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B88" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C88" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="D88" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E88" t="s">
         <v>201</v>
@@ -4521,13 +4524,13 @@
         <v>9.20</v>
       </c>
       <c r="H88" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="I88" t="s">
         <v>30</v>
       </c>
       <c r="J88" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="K88" t="n">
         <v>30</v>
@@ -4535,16 +4538,16 @@
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B89" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C89" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="D89" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E89" t="s">
         <v>41</v>
@@ -4556,13 +4559,13 @@
         <v>7.20</v>
       </c>
       <c r="H89" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="I89" t="s">
         <v>94</v>
       </c>
       <c r="J89" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="K89" t="n">
         <v>30</v>

--- a/src/main/resources/static/assets/inventario_ejemplo_kardo.xlsx
+++ b/src/main/resources/static/assets/inventario_ejemplo_kardo.xlsx
@@ -7,13 +7,14 @@
   </bookViews>
   <sheets>
     <sheet name="Inventario" r:id="rId3" sheetId="1"/>
+    <sheet name="Ventas" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="715" uniqueCount="459">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="745" uniqueCount="464">
   <si>
     <t xml:space="preserve">SKU</t>
   </si>
@@ -66,10 +67,10 @@
     <t xml:space="preserve">L-GLO-2610A</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2027-06-19</t>
+    <t xml:space="preserve">2026-08-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2027-06-20</t>
   </si>
   <si>
     <t xml:space="preserve">LAC-GLO-002</t>
@@ -84,10 +85,10 @@
     <t xml:space="preserve">L-GLO-2610B</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2027-06-29</t>
+    <t xml:space="preserve">2026-09-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2027-06-30</t>
   </si>
   <si>
     <t xml:space="preserve">LAC-GLO-003</t>
@@ -105,10 +106,10 @@
     <t xml:space="preserve">L-GLO-2609U</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2027-03-11</t>
+    <t xml:space="preserve">2026-09-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2027-03-12</t>
   </si>
   <si>
     <t xml:space="preserve">LAC-LAI-004</t>
@@ -123,10 +124,10 @@
     <t xml:space="preserve">L-LAI-2609S</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2027-03-16</t>
+    <t xml:space="preserve">2026-09-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2027-03-17</t>
   </si>
   <si>
     <t xml:space="preserve">LAC-GLO-005</t>
@@ -144,1252 +145,1267 @@
     <t xml:space="preserve">L-YOG-2610F</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04</t>
+    <t xml:space="preserve">2026-10-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LAC-GLO-006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7750101001067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yogurt Gloria Batido Vainilla Botella 1kg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-YOG-2610V</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LAC-LAI-007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7750101001074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yogurt Griego Laive Natural 120g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VASO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-YOG-GR-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-11-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LAC-GLO-008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7750101001081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mantequilla Gloria con Sal 200g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAQUETE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-MAN-2608G</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2027-02-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LAC-LAI-009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7750101001098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mantequilla Laive Pote 225g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POTE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-MAN-2608L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2027-02-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LAC-BON-010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7750101001104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Queso Edam Bonle Rebanado 200g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-QED-2610B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-11-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LAC-LAI-011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7750101001111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Queso Fresco Pasteurizado Laive 400g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EMPAQUE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-QFR-2610L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LAC-GLO-012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7750101001128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crema de Leche Gloria UHT 200ml</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-CRM-2607A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2027-04-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BEB-INC-001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7750102002019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gaseosa Inca Kola Sabor Original 500ml</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BEBIDAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-IK-500-26A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2027-07-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BEB-INC-002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7750102002026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gaseosa Inca Kola Sin Azucar 500ml</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-IK-ZERO-26B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2027-07-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BEB-COC-003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7750102002033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gaseosa Coca Cola Sabor Original 500ml</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-CC-500-26A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BEB-COC-004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7750102002040</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gaseosa Coca Cola Sin Azucar 500ml</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-CC-ZERO-26B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2027-07-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BEB-INC-005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7750102002057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gaseosa Inca Kola Gordita Vidrio 750ml</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-IK-GOR-26C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2027-08-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BEB-SPR-006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7750102002064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gaseosa Sprite Lima-Limon 500ml</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-SP-500-26A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2027-07-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BEB-SLU-007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7750102002071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agua Mineral San Luis Sin Gas 625ml</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-AG-SL-625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2027-10-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BEB-SMA-008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7750102002088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agua Mineral San Mateo con Gas 600ml</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-AG-SM-600</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BEB-SPO-009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7750102002095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bebida Rehidratante Sporade Frutos Rojos 500ml</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-SPO-FR-500</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BEB-GAT-010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7750102002101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bebida Rehidratante Gatorade Cool Blue 500ml</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-GAT-CB-500</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BEB-CIF-011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7750102002118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bebida Citrica Cifrut Granadilla 500ml</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-CIF-GR-500</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2027-05-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BEB-FRU-012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7750102002125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nectar Frugos del Valle Durazno 1L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-FRU-DZ-1L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIC-CUS-001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7750103003016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cerveza Cusquena Dorada Botella 330ml</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LICORES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-CUS-DOR-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIC-CUS-002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7750103003023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cerveza Cusquena Negra Botella 330ml</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-CUS-NEG-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIC-PIL-003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7750103003030</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cerveza Pilsen Callao Botella 630ml</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-PIL-630-26A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIC-PIL-004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7750103003047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cerveza Pilsen Callao Six Pack Lata 355ml</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PACK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-PIL-SIX-26B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2027-08-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIC-CRI-005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7750103003054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cerveza Cristal Botella 650ml</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-CRI-650-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIC-COR-006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7750103003061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cerveza Corona Extra Botella 355ml</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-COR-355-MEX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIC-STE-007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7750103003078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cerveza Stella Artois Botella 330ml</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-STE-330-BEL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2027-08-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIC-CAR-008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7750103003085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ron Cartavio Black Barrel 750ml</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-RON-CAR-BB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2028-10-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIC-GAL-009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7750103003092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pisco Cuatro Gallos Quebranta 700ml</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-PIS-4G-QUE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIC-JOH-010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7750103003108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Whisky Johnnie Walker Red Label 750ml</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-JW-RED-750</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2029-07-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SNK-LAY-001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7750104004013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Papas Fritas Lays Clasicas 160g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SNACKS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BOLSA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-LAY-CLA-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2027-01-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SNK-LAY-002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7750104004020</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Papas Fritas Lays Onduladas 150g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-LAY-OND-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2027-01-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SNK-DOR-003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7750104004037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tortillas de Maiz Doritos Mega Queso 150g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-DOR-QSO-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2027-01-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SNK-CHI-004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7750104004044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Snack de Maiz Chizitos Fiesta 140g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-CHZ-FIE-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-12-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SNK-PIQ-005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7750104004051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Piqueo Snax Familiar 200g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-PIQ-SNX-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2027-01-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SNK-CHI-006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7750104004068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chifle Piurano Salado Karinto 120g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-CHF-KAR-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-12-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SNK-SUB-007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7750104004075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chocolate Sublime Clasico Tableta 30g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UNIDAD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-SUB-CLA-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2027-05-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SNK-PRI-008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7750104004082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chocolate Princesa Crema de Mani 30g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-PRI-CRE-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2027-05-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SNK-TRI-009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7750104004099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chocolate Triangulo DOnofrio 30g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-TRI-DON-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SNK-MOR-010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7750104004105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Galletas Morochas Rellenas Paquete 6 unid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-MOR-PAQ-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2027-03-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SNK-CAS-011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7750104004112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Galletas Casino Menta Paquete 6 unid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-CAS-MEN-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2027-04-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SNK-PEP-012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7750104004129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Galletas Dona Pepa Field Paquete 6 unid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-DNP-PAQ-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SNK-SOD-013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7750104004136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Galletas Soda Field Paquete 6 unid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-SOD-FIE-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SNK-GOM-014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7750104004143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gomitas Ambrosoli Ositos Dulces 100g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-GOM-OSI-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EMB-SFE-001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7750105005010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hot Dog de Pollo San Fernando 500g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EMBUTIDOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-HD-POL-2610</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EMB-SFE-002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7750105005027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jamonada Especial San Fernando 250g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-JAM-SFE-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-11-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EMB-BRA-003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7750105005034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jamonada de Cerdo Braedt 200g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-JAM-BRA-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-11-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EMB-OTT-004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7750105005041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tocino Ahumado Tiras Otto Kunz 180g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-TOC-OTT-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-11-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EMB-SFE-005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7750105005058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chorizo Parrillero San Fernando 400g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-CHO-PAR-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-11-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EMB-PRE-006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7750105005065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Salchicha Huachana La Preferida 250g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-SAL-HUA-26</t>
   </si>
   <si>
     <t xml:space="preserve">2026-10-27</t>
   </si>
   <si>
-    <t xml:space="preserve">LAC-GLO-006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7750101001067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yogurt Gloria Batido Vainilla Botella 1kg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-YOG-2610V</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LAC-LAI-007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7750101001074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yogurt Griego Laive Natural 120g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VASO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-YOG-GR-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-11-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LAC-GLO-008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7750101001081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mantequilla Gloria con Sal 200g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PAQUETE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-MAN-2608G</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2027-02-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LAC-LAI-009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7750101001098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mantequilla Laive Pote 225g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POTE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-MAN-2608L</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2027-02-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LAC-BON-010</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7750101001104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Queso Edam Bonle Rebanado 200g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-QED-2610B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-11-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LAC-LAI-011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7750101001111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Queso Fresco Pasteurizado Laive 400g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EMPAQUE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-QFR-2610L</t>
+    <t xml:space="preserve">EMB-OTT-007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7750105005072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cabanossi Clasico Otto Kunz 100g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-CAB-OTT-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-12-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EMB-BRA-008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7750105005089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jamon del Pais Braedt Laminado 150g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-JPA-BRA-26</t>
   </si>
   <si>
     <t xml:space="preserve">2026-10-12</t>
   </si>
   <si>
+    <t xml:space="preserve">PAN-BIM-001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7750106006017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pan de Molde Blanco Bimbo Grande 750g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PANADERIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-PAN-BLA-2610</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAN-BIM-002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7750106006024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pan de Molde Integral Bimbo 700g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-PAN-INT-2610</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAN-BIM-003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7750106006031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pan Artesano Original Bimbo 550g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-PAN-ART-2610</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAN-BIM-004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7750106006048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pan Hamburguesa con Ajonjoli Bimbo 4 unid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-PAN-HAM-2610</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAN-BIM-005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7750106006055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pan Hot Dog Bimbo 6 unid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-PAN-HD-2610</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAN-BIM-006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7750106006062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Queque Bimbolete Vainilla Bimbo 6 unid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-BIM-VAI-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-11-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAN-BIM-007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7750106006079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tostadas Clasicas Bimbo 180g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-TOS-CLA-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2027-01-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAN-CHA-008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7750106006086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bizcocho Chancay Tradicional 4 unid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-BIZ-CHA-2610</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-19</t>
+  </si>
+  <si>
     <t xml:space="preserve">2026-10-24</t>
   </si>
   <si>
-    <t xml:space="preserve">LAC-GLO-012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7750101001128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Crema de Leche Gloria UHT 200ml</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-CRM-2607A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2027-04-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BEB-INC-001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7750102002019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gaseosa Inca Kola Sabor Original 500ml</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BEBIDAS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-IK-500-26A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2027-07-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BEB-INC-002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7750102002026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gaseosa Inca Kola Sin Azucar 500ml</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-IK-ZERO-26B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2027-07-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BEB-COC-003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7750102002033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gaseosa Coca Cola Sabor Original 500ml</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-CC-500-26A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BEB-COC-004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7750102002040</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gaseosa Coca Cola Sin Azucar 500ml</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-CC-ZERO-26B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2027-07-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BEB-INC-005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7750102002057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gaseosa Inca Kola Gordita Vidrio 750ml</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-IK-GOR-26C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2027-08-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BEB-SPR-006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7750102002064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gaseosa Sprite Lima-Limon 500ml</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-SP-500-26A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2027-07-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BEB-SLU-007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7750102002071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Agua Mineral San Luis Sin Gas 625ml</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-AG-SL-625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2027-10-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BEB-SMA-008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7750102002088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Agua Mineral San Mateo con Gas 600ml</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-AG-SM-600</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BEB-SPO-009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7750102002095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bebida Rehidratante Sporade Frutos Rojos 500ml</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-SPO-FR-500</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BEB-GAT-010</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7750102002101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bebida Rehidratante Gatorade Cool Blue 500ml</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-GAT-CB-500</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BEB-CIF-011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7750102002118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bebida Citrica Cifrut Granadilla 500ml</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-CIF-GR-500</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2027-05-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BEB-FRU-012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7750102002125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nectar Frugos del Valle Durazno 1L</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-FRU-DZ-1L</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIC-CUS-001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7750103003016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cerveza Cusquena Dorada Botella 330ml</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LICORES</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-CUS-DOR-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIC-CUS-002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7750103003023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cerveza Cusquena Negra Botella 330ml</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-CUS-NEG-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIC-PIL-003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7750103003030</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cerveza Pilsen Callao Botella 630ml</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-PIL-630-26A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIC-PIL-004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7750103003047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cerveza Pilsen Callao Six Pack Lata 355ml</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PACK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-PIL-SIX-26B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2027-08-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIC-CRI-005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7750103003054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cerveza Cristal Botella 650ml</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-CRI-650-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIC-COR-006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7750103003061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cerveza Corona Extra Botella 355ml</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-COR-355-MEX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIC-STE-007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7750103003078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cerveza Stella Artois Botella 330ml</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-STE-330-BEL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2027-08-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIC-CAR-008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7750103003085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ron Cartavio Black Barrel 750ml</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-RON-CAR-BB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2028-10-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIC-GAL-009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7750103003092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pisco Cuatro Gallos Quebranta 700ml</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-PIS-4G-QUE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIC-JOH-010</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7750103003108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Whisky Johnnie Walker Red Label 750ml</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-JW-RED-750</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-04-25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2029-07-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SNK-LAY-001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7750104004013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Papas Fritas Lays Clasicas 160g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SNACKS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BOLSA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-LAY-CLA-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2027-01-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SNK-LAY-002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7750104004020</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Papas Fritas Lays Onduladas 150g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-LAY-OND-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-12-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SNK-DOR-003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7750104004037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tortillas de Maiz Doritos Mega Queso 150g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-DOR-QSO-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2027-01-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SNK-CHI-004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7750104004044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Snack de Maiz Chizitos Fiesta 140g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-CHZ-FIE-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-12-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SNK-PIQ-005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7750104004051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Piqueo Snax Familiar 200g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-PIQ-SNX-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2027-01-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SNK-CHI-006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7750104004068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chifle Piurano Salado Karinto 120g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-CHF-KAR-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-12-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SNK-SUB-007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7750104004075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chocolate Sublime Clasico Tableta 30g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UNIDAD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-SUB-CLA-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2027-05-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SNK-PRI-008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7750104004082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chocolate Princesa Crema de Mani 30g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-PRI-CRE-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2027-04-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SNK-TRI-009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7750104004099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chocolate Triangulo DOnofrio 30g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-TRI-DON-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SNK-MOR-010</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7750104004105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Galletas Morochas Rellenas Paquete 6 unid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-MOR-PAQ-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2027-03-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SNK-CAS-011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7750104004112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Galletas Casino Menta Paquete 6 unid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-CAS-MEN-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2027-03-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SNK-PEP-012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7750104004129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Galletas Dona Pepa Field Paquete 6 unid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-DNP-PAQ-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SNK-SOD-013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7750104004136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Galletas Soda Field Paquete 6 unid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-SOD-FIE-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SNK-GOM-014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7750104004143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gomitas Ambrosoli Ositos Dulces 100g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-GOM-OSI-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EMB-SFE-001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7750105005010</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hot Dog de Pollo San Fernando 500g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EMBUTIDOS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-HD-POL-2610</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EMB-SFE-002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7750105005027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jamonada Especial San Fernando 250g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-JAM-SFE-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EMB-BRA-003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7750105005034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jamonada de Cerdo Braedt 200g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-JAM-BRA-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-11-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EMB-OTT-004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7750105005041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tocino Ahumado Tiras Otto Kunz 180g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-TOC-OTT-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-11-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EMB-SFE-005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7750105005058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chorizo Parrillero San Fernando 400g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-CHO-PAR-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-11-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EMB-PRE-006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7750105005065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Salchicha Huachana La Preferida 250g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-SAL-HUA-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EMB-OTT-007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7750105005072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cabanossi Clasico Otto Kunz 100g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-CAB-OTT-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-12-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EMB-BRA-008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7750105005089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jamon del Pais Braedt Laminado 150g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-JPA-BRA-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PAN-BIM-001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7750106006017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pan de Molde Blanco Bimbo Grande 750g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PANADERIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-PAN-BLA-2610</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PAN-BIM-002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7750106006024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pan de Molde Integral Bimbo 700g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-PAN-INT-2610</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PAN-BIM-003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7750106006031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pan Artesano Original Bimbo 550g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-PAN-ART-2610</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PAN-BIM-004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7750106006048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pan Hamburguesa con Ajonjoli Bimbo 4 unid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-PAN-HAM-2610</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PAN-BIM-005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7750106006055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pan Hot Dog Bimbo 6 unid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-PAN-HD-2610</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PAN-BIM-006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7750106006062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Queque Bimbolete Vainilla Bimbo 6 unid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-BIM-VAI-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-11-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PAN-BIM-007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7750106006079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tostadas Clasicas Bimbo 180g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-TOS-CLA-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2027-01-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PAN-CHA-008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7750106006086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bizcocho Chancay Tradicional 4 unid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-BIZ-CHA-2610</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-18</t>
+    <t xml:space="preserve">ABA-COS-001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7750107007014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arroz Superior Costeno Bolsa 1kg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ABARROTES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-ARR-SUP-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ABA-COS-002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7750107007021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arroz Extra Costeno Bolsa 1kg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-ARR-EXT-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ABA-PRI-003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7750107007038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aceite Vegetal Primor Clasico Botella 900ml</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-ACE-PRI-900</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ABA-OLI-004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7750107007045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aceite de Oliva Extra Virgen Huerto Alamein 500ml</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-ACE-OLI-500</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2028-03-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ABA-VIT-005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7750107007052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fideos Spaghetti Don Vittorio 450g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-FID-SPA-450</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2027-11-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ABA-LAV-006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7750107007069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fideos Tornillo Lavaggi 450g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-FID-TOR-450</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ABA-FLO-007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7750107007076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trozos de Atun en Aceite Vegetal Florida 140g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-ATU-FLO-140</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ABA-GLO-008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7750107007083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Filete de Atun en Aceite de Oliva Gloria 140g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-ATU-GLO-140</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ABA-ALA-009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7750107007090</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mayonesa Alacena Doypack 475g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DOYPACK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-MAY-ALA-475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ABA-ALA-010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7750107007106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ketchup Alacena Doypack 380g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-KET-ALA-380</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ABA-TAR-011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7750107007113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crema de Aji Tari Alacena Doypack 400g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-TAR-ALA-400</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ABA-NES-012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7750107007120</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cafe Instantaneo Nescafe Tradicion Frasco 100g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FRASCO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-CAF-NES-100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2028-04-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIM-SUA-001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7750108008011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Papel Higienico Suave Rendidor Doble Hoja 4 rollos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIMPIEZA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-PH-SUA-4R</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIM-ELI-002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7750108008028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Papel Higienico Elite Duplex 4 rollos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-PH-ELI-4R</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIM-ELI-003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7750108008035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Papel Toalla Elite Ultra 2 rollos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-PT-ELI-2R</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIM-DOV-004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7750108008042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jabon de Tocador Dove Original Barra 90g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-JAB-DOV-90</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIM-PRO-005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7750108008059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jabon Antibacterial Protex Aloe Barra 110g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-JAB-PRO-110</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIM-SED-006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7750108008066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shampoo Sedal Restauracion Instantanea 340ml</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-SHA-SED-340</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIM-COL-007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7750108008073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crema Dental Colgate Triple Accion Tubo 75ml</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUBO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-DEN-COL-75</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIM-CLO-008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7750108008080</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lejia Tradicional Clorox Botella 1L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-LEJ-CLO-1L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIM-SAP-009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7750108008097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lavavajillas en Crema Sapolio Limon Pote 450g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-LAV-SAP-450</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIM-POE-010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7750108008103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Limpiador Liquido Poett Lavanda Botella 900ml</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-POE-LAV-900</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIM-ACE-011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7750108008110</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Detergente en Polvo Ace Floral Bolsa 800g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-DET-ACE-800</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIM-AYU-012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7750108008127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lavavajillas Liquido Ayudin Limon Botella 500ml</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L-AYU-LIQ-500</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fecha</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-22</t>
   </si>
   <si>
     <t xml:space="preserve">2026-10-23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ABA-COS-001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7750107007014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arroz Superior Costeno Bolsa 1kg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ABARROTES</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-ARR-SUP-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ABA-COS-002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7750107007021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arroz Extra Costeno Bolsa 1kg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-ARR-EXT-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ABA-PRI-003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7750107007038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aceite Vegetal Primor Clasico Botella 900ml</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-ACE-PRI-900</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ABA-OLI-004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7750107007045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aceite de Oliva Extra Virgen Huerto Alamein 500ml</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-ACE-OLI-500</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2028-03-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ABA-VIT-005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7750107007052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fideos Spaghetti Don Vittorio 450g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-FID-SPA-450</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2027-11-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ABA-LAV-006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7750107007069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fideos Tornillo Lavaggi 450g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-FID-TOR-450</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ABA-FLO-007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7750107007076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trozos de Atun en Aceite Vegetal Florida 140g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-ATU-FLO-140</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ABA-GLO-008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7750107007083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Filete de Atun en Aceite de Oliva Gloria 140g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-ATU-GLO-140</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ABA-ALA-009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7750107007090</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mayonesa Alacena Doypack 475g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DOYPACK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-MAY-ALA-475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ABA-ALA-010</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7750107007106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ketchup Alacena Doypack 380g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-KET-ALA-380</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ABA-TAR-011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7750107007113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Crema de Aji Tari Alacena Doypack 400g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-TAR-ALA-400</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ABA-NES-012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7750107007120</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cafe Instantaneo Nescafe Tradicion Frasco 100g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FRASCO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-CAF-NES-100</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2028-04-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIM-SUA-001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7750108008011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Papel Higienico Suave Rendidor Doble Hoja 4 rollos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIMPIEZA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-PH-SUA-4R</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIM-ELI-002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7750108008028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Papel Higienico Elite Duplex 4 rollos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-PH-ELI-4R</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIM-ELI-003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7750108008035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Papel Toalla Elite Ultra 2 rollos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-PT-ELI-2R</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIM-DOV-004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7750108008042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jabon de Tocador Dove Original Barra 90g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-JAB-DOV-90</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIM-PRO-005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7750108008059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jabon Antibacterial Protex Aloe Barra 110g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-JAB-PRO-110</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIM-SED-006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7750108008066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shampoo Sedal Restauracion Instantanea 340ml</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-SHA-SED-340</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIM-COL-007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7750108008073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Crema Dental Colgate Triple Accion Tubo 75ml</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUBO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-DEN-COL-75</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIM-CLO-008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7750108008080</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lejia Tradicional Clorox Botella 1L</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-LEJ-CLO-1L</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIM-SAP-009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7750108008097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lavavajillas en Crema Sapolio Limon Pote 450g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-LAV-SAP-450</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIM-POE-010</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7750108008103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Limpiador Liquido Poett Lavanda Botella 900ml</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-POE-LAV-900</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIM-ACE-011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7750108008110</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Detergente en Polvo Ace Floral Bolsa 800g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-DET-ACE-800</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIM-AYU-012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7750108008127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lavavajillas Liquido Ayudin Limon Botella 500ml</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L-AYU-LIQ-500</t>
   </si>
 </sst>
 </file>
@@ -4579,4 +4595,189 @@
     <oddFooter/>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false" autoPageBreaks="false"/>
+  </sheetPr>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="18.0" outlineLevel="0" customWidth="true" bestFit="false"/>
+    <col min="2" max="2" width="10.0" outlineLevel="0" customWidth="true" bestFit="false"/>
+    <col min="3" max="3" width="14.0" outlineLevel="0" customWidth="true" bestFit="false"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>89</v>
+      </c>
+      <c r="B2" t="n">
+        <v>12</v>
+      </c>
+      <c r="C2" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>101</v>
+      </c>
+      <c r="B3" t="n">
+        <v>9</v>
+      </c>
+      <c r="C3" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>121</v>
+      </c>
+      <c r="B4" t="n">
+        <v>15</v>
+      </c>
+      <c r="C4" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>230</v>
+      </c>
+      <c r="B5" t="n">
+        <v>6</v>
+      </c>
+      <c r="C5" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>89</v>
+      </c>
+      <c r="B6" t="n">
+        <v>10</v>
+      </c>
+      <c r="C6" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>352</v>
+      </c>
+      <c r="B7" t="n">
+        <v>8</v>
+      </c>
+      <c r="C7" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" t="n">
+        <v>6</v>
+      </c>
+      <c r="C8" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>89</v>
+      </c>
+      <c r="B9" t="n">
+        <v>14</v>
+      </c>
+      <c r="C9" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>126</v>
+      </c>
+      <c r="B10" t="n">
+        <v>7</v>
+      </c>
+      <c r="C10" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>156</v>
+      </c>
+      <c r="B11" t="n">
+        <v>4</v>
+      </c>
+      <c r="C11" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>236</v>
+      </c>
+      <c r="B12" t="n">
+        <v>5</v>
+      </c>
+      <c r="C12" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>101</v>
+      </c>
+      <c r="B13" t="n">
+        <v>11</v>
+      </c>
+      <c r="C13" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>379</v>
+      </c>
+      <c r="B14" t="n">
+        <v>9</v>
+      </c>
+      <c r="C14" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>11</v>
+      </c>
+      <c r="B15" t="n">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="0" useFirstPageNumber="false" blackAndWhite="false" orientation="portrait"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
 </file>
--- a/src/main/resources/static/assets/inventario_ejemplo_kardo.xlsx
+++ b/src/main/resources/static/assets/inventario_ejemplo_kardo.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="745" uniqueCount="464">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="860" uniqueCount="469">
   <si>
     <t xml:space="preserve">SKU</t>
   </si>
@@ -1399,10 +1399,25 @@
     <t xml:space="preserve">2026-10-20</t>
   </si>
   <si>
+    <t xml:space="preserve">BEB-VOL-010</t>
+  </si>
+  <si>
     <t xml:space="preserve">2026-10-21</t>
   </si>
   <si>
+    <t xml:space="preserve">BEB-CIF-014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LAC-NES-011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIC-CRI-004</t>
+  </si>
+  <si>
     <t xml:space="preserve">2026-10-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BEB-SCA-009</t>
   </si>
   <si>
     <t xml:space="preserve">2026-10-23</t>
@@ -4626,10 +4641,10 @@
         <v>89</v>
       </c>
       <c r="B2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C2" t="s">
-        <v>460</v>
+        <v>350</v>
       </c>
     </row>
     <row r="3">
@@ -4637,10 +4652,10 @@
         <v>101</v>
       </c>
       <c r="B3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>460</v>
+        <v>350</v>
       </c>
     </row>
     <row r="4">
@@ -4648,10 +4663,10 @@
         <v>121</v>
       </c>
       <c r="B4" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C4" t="s">
-        <v>460</v>
+        <v>350</v>
       </c>
     </row>
     <row r="5">
@@ -4659,117 +4674,752 @@
         <v>230</v>
       </c>
       <c r="B5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C5" t="s">
-        <v>460</v>
+        <v>350</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>89</v>
+        <v>197</v>
       </c>
       <c r="B6" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C6" t="s">
-        <v>461</v>
+        <v>350</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>352</v>
+        <v>11</v>
       </c>
       <c r="B7" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C7" t="s">
-        <v>461</v>
+        <v>350</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="B8" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C8" t="s">
-        <v>461</v>
+        <v>350</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>89</v>
+        <v>267</v>
       </c>
       <c r="B9" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="C9" t="s">
-        <v>462</v>
+        <v>350</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>126</v>
+        <v>310</v>
       </c>
       <c r="B10" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C10" t="s">
-        <v>462</v>
+        <v>350</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>156</v>
+        <v>327</v>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C11" t="s">
-        <v>462</v>
+        <v>350</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>236</v>
+        <v>352</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C12" t="s">
-        <v>462</v>
+        <v>350</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>101</v>
+        <v>379</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C13" t="s">
-        <v>463</v>
+        <v>350</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>379</v>
+        <v>156</v>
       </c>
       <c r="B14" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C14" t="s">
-        <v>463</v>
+        <v>350</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>11</v>
+        <v>439</v>
       </c>
       <c r="B15" t="n">
         <v>4</v>
+      </c>
+      <c r="C15" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>408</v>
+      </c>
+      <c r="B16" t="n">
+        <v>3</v>
+      </c>
+      <c r="C16" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>89</v>
+      </c>
+      <c r="B17" t="n">
+        <v>12</v>
+      </c>
+      <c r="C17" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>96</v>
+      </c>
+      <c r="B18" t="n">
+        <v>5</v>
+      </c>
+      <c r="C18" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>101</v>
+      </c>
+      <c r="B19" t="n">
+        <v>9</v>
+      </c>
+      <c r="C19" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>461</v>
+      </c>
+      <c r="B20" t="n">
+        <v>6</v>
+      </c>
+      <c r="C20" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>236</v>
+      </c>
+      <c r="B21" t="n">
+        <v>6</v>
+      </c>
+      <c r="C21" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>210</v>
+      </c>
+      <c r="B22" t="n">
+        <v>4</v>
+      </c>
+      <c r="C22" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>11</v>
+      </c>
+      <c r="B23" t="n">
+        <v>5</v>
+      </c>
+      <c r="C23" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>51</v>
+      </c>
+      <c r="B24" t="n">
+        <v>4</v>
+      </c>
+      <c r="C24" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>273</v>
+      </c>
+      <c r="B25" t="n">
+        <v>3</v>
+      </c>
+      <c r="C25" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>300</v>
+      </c>
+      <c r="B26" t="n">
+        <v>2</v>
+      </c>
+      <c r="C26" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>316</v>
+      </c>
+      <c r="B27" t="n">
+        <v>2</v>
+      </c>
+      <c r="C27" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>332</v>
+      </c>
+      <c r="B28" t="n">
+        <v>3</v>
+      </c>
+      <c r="C28" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>361</v>
+      </c>
+      <c r="B29" t="n">
+        <v>4</v>
+      </c>
+      <c r="C29" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>370</v>
+      </c>
+      <c r="B30" t="n">
+        <v>6</v>
+      </c>
+      <c r="C30" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>147</v>
+      </c>
+      <c r="B31" t="n">
+        <v>6</v>
+      </c>
+      <c r="C31" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>89</v>
+      </c>
+      <c r="B32" t="n">
+        <v>10</v>
+      </c>
+      <c r="C32" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>126</v>
+      </c>
+      <c r="B33" t="n">
+        <v>5</v>
+      </c>
+      <c r="C33" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>463</v>
+      </c>
+      <c r="B34" t="n">
+        <v>7</v>
+      </c>
+      <c r="C34" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>230</v>
+      </c>
+      <c r="B35" t="n">
+        <v>7</v>
+      </c>
+      <c r="C35" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>250</v>
+      </c>
+      <c r="B36" t="n">
+        <v>5</v>
+      </c>
+      <c r="C36" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>259</v>
+      </c>
+      <c r="B37" t="n">
+        <v>6</v>
+      </c>
+      <c r="C37" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s">
+        <v>19</v>
+      </c>
+      <c r="B38" t="n">
+        <v>4</v>
+      </c>
+      <c r="C38" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s">
+        <v>464</v>
+      </c>
+      <c r="B39" t="n">
+        <v>3</v>
+      </c>
+      <c r="C39" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s">
+        <v>279</v>
+      </c>
+      <c r="B40" t="n">
+        <v>2</v>
+      </c>
+      <c r="C40" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s">
+        <v>290</v>
+      </c>
+      <c r="B41" t="n">
+        <v>2</v>
+      </c>
+      <c r="C41" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s">
+        <v>310</v>
+      </c>
+      <c r="B42" t="n">
+        <v>2</v>
+      </c>
+      <c r="C42" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s">
+        <v>336</v>
+      </c>
+      <c r="B43" t="n">
+        <v>3</v>
+      </c>
+      <c r="C43" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s">
+        <v>352</v>
+      </c>
+      <c r="B44" t="n">
+        <v>8</v>
+      </c>
+      <c r="C44" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s">
+        <v>388</v>
+      </c>
+      <c r="B45" t="n">
+        <v>4</v>
+      </c>
+      <c r="C45" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s">
+        <v>465</v>
+      </c>
+      <c r="B46" t="n">
+        <v>8</v>
+      </c>
+      <c r="C46" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s">
+        <v>421</v>
+      </c>
+      <c r="B47" t="n">
+        <v>4</v>
+      </c>
+      <c r="C47" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s">
+        <v>89</v>
+      </c>
+      <c r="B48" t="n">
+        <v>14</v>
+      </c>
+      <c r="C48" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s">
+        <v>101</v>
+      </c>
+      <c r="B49" t="n">
+        <v>10</v>
+      </c>
+      <c r="C49" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s">
+        <v>105</v>
+      </c>
+      <c r="B50" t="n">
+        <v>4</v>
+      </c>
+      <c r="C50" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s">
+        <v>467</v>
+      </c>
+      <c r="B51" t="n">
+        <v>8</v>
+      </c>
+      <c r="C51" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s">
+        <v>241</v>
+      </c>
+      <c r="B52" t="n">
+        <v>6</v>
+      </c>
+      <c r="C52" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s">
+        <v>255</v>
+      </c>
+      <c r="B53" t="n">
+        <v>4</v>
+      </c>
+      <c r="C53" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s">
+        <v>11</v>
+      </c>
+      <c r="B54" t="n">
+        <v>6</v>
+      </c>
+      <c r="C54" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s">
+        <v>71</v>
+      </c>
+      <c r="B55" t="n">
+        <v>5</v>
+      </c>
+      <c r="C55" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s">
+        <v>267</v>
+      </c>
+      <c r="B56" t="n">
+        <v>3</v>
+      </c>
+      <c r="C56" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s">
+        <v>284</v>
+      </c>
+      <c r="B57" t="n">
+        <v>2</v>
+      </c>
+      <c r="C57" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s">
+        <v>322</v>
+      </c>
+      <c r="B58" t="n">
+        <v>2</v>
+      </c>
+      <c r="C58" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s">
+        <v>341</v>
+      </c>
+      <c r="B59" t="n">
+        <v>3</v>
+      </c>
+      <c r="C59" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s">
+        <v>357</v>
+      </c>
+      <c r="B60" t="n">
+        <v>6</v>
+      </c>
+      <c r="C60" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s">
+        <v>383</v>
+      </c>
+      <c r="B61" t="n">
+        <v>4</v>
+      </c>
+      <c r="C61" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s">
+        <v>156</v>
+      </c>
+      <c r="B62" t="n">
+        <v>8</v>
+      </c>
+      <c r="C62" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s">
+        <v>443</v>
+      </c>
+      <c r="B63" t="n">
+        <v>3</v>
+      </c>
+      <c r="C63" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s">
+        <v>89</v>
+      </c>
+      <c r="B64" t="n">
+        <v>8</v>
+      </c>
+      <c r="C64" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s">
+        <v>101</v>
+      </c>
+      <c r="B65" t="n">
+        <v>11</v>
+      </c>
+      <c r="C65" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s">
+        <v>121</v>
+      </c>
+      <c r="B66" t="n">
+        <v>10</v>
+      </c>
+      <c r="C66" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s">
+        <v>230</v>
+      </c>
+      <c r="B67" t="n">
+        <v>6</v>
+      </c>
+      <c r="C67" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s">
+        <v>11</v>
+      </c>
+      <c r="B68" t="n">
+        <v>4</v>
+      </c>
+      <c r="C68" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s">
+        <v>267</v>
+      </c>
+      <c r="B69" t="n">
+        <v>2</v>
+      </c>
+      <c r="C69" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s">
+        <v>310</v>
+      </c>
+      <c r="B70" t="n">
+        <v>2</v>
+      </c>
+      <c r="C70" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s">
+        <v>379</v>
+      </c>
+      <c r="B71" t="n">
+        <v>6</v>
+      </c>
+      <c r="C71" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s">
+        <v>352</v>
+      </c>
+      <c r="B72" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s">
+        <v>89</v>
+      </c>
+      <c r="B73" t="n">
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/static/assets/inventario_ejemplo_kardo.xlsx
+++ b/src/main/resources/static/assets/inventario_ejemplo_kardo.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="860" uniqueCount="469">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="860" uniqueCount="464">
   <si>
     <t xml:space="preserve">SKU</t>
   </si>
@@ -1399,25 +1399,10 @@
     <t xml:space="preserve">2026-10-20</t>
   </si>
   <si>
-    <t xml:space="preserve">BEB-VOL-010</t>
-  </si>
-  <si>
     <t xml:space="preserve">2026-10-21</t>
   </si>
   <si>
-    <t xml:space="preserve">BEB-CIF-014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LAC-NES-011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIC-CRI-004</t>
-  </si>
-  <si>
     <t xml:space="preserve">2026-10-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BEB-SCA-009</t>
   </si>
   <si>
     <t xml:space="preserve">2026-10-23</t>
@@ -4836,7 +4821,7 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>461</v>
+        <v>134</v>
       </c>
       <c r="B20" t="n">
         <v>6</v>
@@ -4974,7 +4959,7 @@
         <v>10</v>
       </c>
       <c r="C32" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="33">
@@ -4985,18 +4970,18 @@
         <v>5</v>
       </c>
       <c r="C33" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>463</v>
+        <v>138</v>
       </c>
       <c r="B34" t="n">
         <v>7</v>
       </c>
       <c r="C34" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="35">
@@ -5007,7 +4992,7 @@
         <v>7</v>
       </c>
       <c r="C35" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="36">
@@ -5018,7 +5003,7 @@
         <v>5</v>
       </c>
       <c r="C36" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="37">
@@ -5029,7 +5014,7 @@
         <v>6</v>
       </c>
       <c r="C37" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="38">
@@ -5040,18 +5025,18 @@
         <v>4</v>
       </c>
       <c r="C38" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>464</v>
+        <v>58</v>
       </c>
       <c r="B39" t="n">
         <v>3</v>
       </c>
       <c r="C39" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="40">
@@ -5062,7 +5047,7 @@
         <v>2</v>
       </c>
       <c r="C40" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="41">
@@ -5073,7 +5058,7 @@
         <v>2</v>
       </c>
       <c r="C41" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="42">
@@ -5084,7 +5069,7 @@
         <v>2</v>
       </c>
       <c r="C42" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="43">
@@ -5095,7 +5080,7 @@
         <v>3</v>
       </c>
       <c r="C43" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="44">
@@ -5106,7 +5091,7 @@
         <v>8</v>
       </c>
       <c r="C44" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="45">
@@ -5117,18 +5102,18 @@
         <v>4</v>
       </c>
       <c r="C45" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>465</v>
+        <v>166</v>
       </c>
       <c r="B46" t="n">
         <v>8</v>
       </c>
       <c r="C46" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="47">
@@ -5139,7 +5124,7 @@
         <v>4</v>
       </c>
       <c r="C47" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="48">
@@ -5150,7 +5135,7 @@
         <v>14</v>
       </c>
       <c r="C48" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
     </row>
     <row r="49">
@@ -5161,7 +5146,7 @@
         <v>10</v>
       </c>
       <c r="C49" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
     </row>
     <row r="50">
@@ -5172,18 +5157,18 @@
         <v>4</v>
       </c>
       <c r="C50" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>467</v>
+        <v>130</v>
       </c>
       <c r="B51" t="n">
         <v>8</v>
       </c>
       <c r="C51" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
     </row>
     <row r="52">
@@ -5194,7 +5179,7 @@
         <v>6</v>
       </c>
       <c r="C52" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
     </row>
     <row r="53">
@@ -5205,7 +5190,7 @@
         <v>4</v>
       </c>
       <c r="C53" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
     </row>
     <row r="54">
@@ -5216,7 +5201,7 @@
         <v>6</v>
       </c>
       <c r="C54" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
     </row>
     <row r="55">
@@ -5227,7 +5212,7 @@
         <v>5</v>
       </c>
       <c r="C55" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
     </row>
     <row r="56">
@@ -5238,7 +5223,7 @@
         <v>3</v>
       </c>
       <c r="C56" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
     </row>
     <row r="57">
@@ -5249,7 +5234,7 @@
         <v>2</v>
       </c>
       <c r="C57" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
     </row>
     <row r="58">
@@ -5260,7 +5245,7 @@
         <v>2</v>
       </c>
       <c r="C58" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
     </row>
     <row r="59">
@@ -5271,7 +5256,7 @@
         <v>3</v>
       </c>
       <c r="C59" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
     </row>
     <row r="60">
@@ -5282,7 +5267,7 @@
         <v>6</v>
       </c>
       <c r="C60" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
     </row>
     <row r="61">
@@ -5293,7 +5278,7 @@
         <v>4</v>
       </c>
       <c r="C61" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
     </row>
     <row r="62">
@@ -5304,7 +5289,7 @@
         <v>8</v>
       </c>
       <c r="C62" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
     </row>
     <row r="63">
@@ -5315,7 +5300,7 @@
         <v>3</v>
       </c>
       <c r="C63" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
     </row>
     <row r="64">
@@ -5326,7 +5311,7 @@
         <v>8</v>
       </c>
       <c r="C64" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
     </row>
     <row r="65">
@@ -5337,7 +5322,7 @@
         <v>11</v>
       </c>
       <c r="C65" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
     </row>
     <row r="66">
@@ -5348,7 +5333,7 @@
         <v>10</v>
       </c>
       <c r="C66" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
     </row>
     <row r="67">
@@ -5359,7 +5344,7 @@
         <v>6</v>
       </c>
       <c r="C67" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
     </row>
     <row r="68">
@@ -5370,7 +5355,7 @@
         <v>4</v>
       </c>
       <c r="C68" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
     </row>
     <row r="69">
@@ -5381,7 +5366,7 @@
         <v>2</v>
       </c>
       <c r="C69" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
     </row>
     <row r="70">
@@ -5392,7 +5377,7 @@
         <v>2</v>
       </c>
       <c r="C70" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
     </row>
     <row r="71">
@@ -5403,7 +5388,7 @@
         <v>6</v>
       </c>
       <c r="C71" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
     </row>
     <row r="72">
